--- a/stories/arbres/TREE-SEC-003.xlsx
+++ b/stories/arbres/TREE-SEC-003.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Jules est dans le train avec Papa. Le train roule, doucement. Jules reste près de l'adulte. Sa main tient la main de Papa, ou le manteau de Papa. Ses pieds sont à côté des pieds de Papa. Maman les rejoindra à la gare.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Après le train, Jules et Papa vont au bac à sable du petit square. Jules reste près de l'adulte. Main dans la main de Papa, ou sur le manteau. Pieds à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1869,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On reste où ? Près de l'adulte.</t>
         </is>
       </c>
     </row>
@@ -2009,6 +2046,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules retient : près de l'adulte, main ou manteau. La main tient la main de Papa, ou le manteau de Papa. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2195,6 +2237,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2361,6 +2408,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi les cubes. Le train souffle loin. Jules pose les cubes près de Papa. Il reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2547,6 +2599,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2713,6 +2770,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. Le vent est doux. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2875,6 +2937,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3041,6 +3108,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. Le banc est froid. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3203,6 +3275,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3369,6 +3446,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. Une feuille tombe. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3531,6 +3613,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3697,6 +3784,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le livre. Un oiseau chante. Jules tient le livre contre le manteau de Papa. Il reste près de l'adulte. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3883,6 +3975,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4049,6 +4146,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. Le banc est froid. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4211,6 +4313,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4377,6 +4484,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. Une feuille tombe. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4539,6 +4651,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4705,6 +4822,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. On entend des pas. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4867,6 +4989,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5033,6 +5160,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la dînette. Le vent est doux. Jules range la dînette. Il reste près de l'adulte. Main dans la main de Papa. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5219,6 +5351,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5385,6 +5522,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. Une feuille tombe. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5547,6 +5689,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5713,6 +5860,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. On entend des pas. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5875,6 +6027,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6041,6 +6198,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. Le train souffle loin. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6203,6 +6365,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6369,6 +6536,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Après le train, ils vont près du toboggan. Jules reste près de l'adulte. Main dans la main de Papa, ou sur le manteau. Pieds à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6553,6 +6725,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On reste où ? Près de l'adulte.</t>
         </is>
       </c>
     </row>
@@ -6725,6 +6902,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules retient : près de l'adulte, main ou manteau. La main tient la main de Papa, ou le manteau de Papa. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6911,6 +7093,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7077,6 +7264,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi les cubes. Le banc est froid. Jules pose les cubes près de Papa. Il reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7263,6 +7455,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7429,6 +7626,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. Le banc est froid. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7591,6 +7793,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7757,6 +7964,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. Une feuille tombe. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7919,6 +8131,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8085,6 +8302,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. On entend des pas. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8247,6 +8469,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8413,6 +8640,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le livre. Une feuille tombe. Jules tient le livre contre le manteau de Papa. Il reste près de l'adulte. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8599,6 +8831,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8765,6 +9002,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. Une feuille tombe. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8927,6 +9169,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9093,6 +9340,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. On entend des pas. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9255,6 +9507,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9421,6 +9678,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. Le train souffle loin. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9583,6 +9845,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9749,6 +10016,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la dînette. On entend des pas. Jules range la dînette. Il reste près de l'adulte. Main dans la main de Papa. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9935,6 +10207,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10101,6 +10378,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. On entend des pas. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10263,6 +10545,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10429,6 +10716,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. Le train souffle loin. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10591,6 +10883,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10757,6 +11054,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. Un oiseau chante. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10919,6 +11221,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11085,6 +11392,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Après le train, ils vont près des balançoires. Jules reste près de l'adulte. Main dans la main de Papa, ou sur le manteau. Pieds à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11269,6 +11581,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On reste où ? Près de l'adulte.</t>
         </is>
       </c>
     </row>
@@ -11441,6 +11758,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules retient : près de l'adulte, main ou manteau. La main tient la main de Papa, ou le manteau de Papa. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11627,6 +11949,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11793,6 +12120,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi les cubes. Le train souffle loin. Jules pose les cubes près de Papa. Il reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11979,6 +12311,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12145,6 +12482,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. Une feuille tombe. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12307,6 +12649,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12473,6 +12820,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. On entend des pas. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12635,6 +12987,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12801,6 +13158,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. Le train souffle loin. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12963,6 +13325,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13129,6 +13496,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le livre. Un oiseau chante. Jules tient le livre contre le manteau de Papa. Il reste près de l'adulte. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13315,6 +13687,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13481,6 +13858,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. On entend des pas. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13643,6 +14025,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13809,6 +14196,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. Le train souffle loin. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13971,6 +14363,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14137,6 +14534,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. Un oiseau chante. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14299,6 +14701,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14465,6 +14872,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la dînette. Le vent est doux. Jules range la dînette. Il reste près de l'adulte. Main dans la main de Papa. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14651,6 +15063,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14817,6 +15234,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. Le train souffle loin. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14979,6 +15401,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15145,6 +15572,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. Un oiseau chante. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15307,6 +15739,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15473,6 +15910,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. Le vent est doux. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15635,6 +16077,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15653,7 +16100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15670,6 +16117,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-003.xlsx
+++ b/stories/arbres/TREE-SEC-003.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Jules est dans le train avec Papa. Le train roule, doucement. Jules reste près de l'adulte. Sa main tient la main de Papa, ou le manteau de Papa. Ses pieds sont à côté des pieds de Papa. Maman les rejoindra à la gare.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|Après le train, Jules et Papa vont au bac à sable du petit square. Jules reste près de l'adulte. Main dans la main de Papa, ou sur le manteau. Pieds à côté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1876,6 +1884,7 @@
           <t>narrateur|On reste où ? Près de l'adulte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2051,6 +2060,7 @@
           <t>narrateur|Oui. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules retient : près de l'adulte, main ou manteau. La main tient la main de Papa, ou le manteau de Papa. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2242,6 +2252,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2413,6 +2424,7 @@
           <t>narrateur|Jules a choisi les cubes. Le train souffle loin. Jules pose les cubes près de Papa. Il reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2604,6 +2616,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2775,6 +2788,7 @@
           <t>narrateur|Jules choisit jaune. Le vent est doux. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2942,6 +2956,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3113,6 +3128,7 @@
           <t>narrateur|Jules choisit bleu. Le banc est froid. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3280,6 +3296,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3451,6 +3468,7 @@
           <t>narrateur|Jules choisit blanc. Une feuille tombe. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3618,6 +3636,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3789,6 +3808,7 @@
           <t>narrateur|Jules a choisi le livre. Un oiseau chante. Jules tient le livre contre le manteau de Papa. Il reste près de l'adulte. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3980,6 +4000,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4151,6 +4172,7 @@
           <t>narrateur|Jules choisit jaune. Le banc est froid. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4318,6 +4340,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4489,6 +4512,7 @@
           <t>narrateur|Jules choisit bleu. Une feuille tombe. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4656,6 +4680,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4827,6 +4852,7 @@
           <t>narrateur|Jules choisit blanc. On entend des pas. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4994,6 +5020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5165,6 +5192,7 @@
           <t>narrateur|Jules a choisi la dînette. Le vent est doux. Jules range la dînette. Il reste près de l'adulte. Main dans la main de Papa. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5356,6 +5384,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5527,6 +5556,7 @@
           <t>narrateur|Jules choisit jaune. Une feuille tombe. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5694,6 +5724,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5865,6 +5896,7 @@
           <t>narrateur|Jules choisit bleu. On entend des pas. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6032,6 +6064,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6203,6 +6236,7 @@
           <t>narrateur|Jules choisit blanc. Le train souffle loin. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6370,6 +6404,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6541,6 +6576,7 @@
           <t>narrateur|Après le train, ils vont près du toboggan. Jules reste près de l'adulte. Main dans la main de Papa, ou sur le manteau. Pieds à côté.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6732,6 +6768,7 @@
           <t>narrateur|On reste où ? Près de l'adulte.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6907,6 +6944,7 @@
           <t>narrateur|Oui. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules retient : près de l'adulte, main ou manteau. La main tient la main de Papa, ou le manteau de Papa. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7098,6 +7136,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7269,6 +7308,7 @@
           <t>narrateur|Jules a choisi les cubes. Le banc est froid. Jules pose les cubes près de Papa. Il reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7460,6 +7500,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7631,6 +7672,7 @@
           <t>narrateur|Jules choisit jaune. Le banc est froid. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7798,6 +7840,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7969,6 +8012,7 @@
           <t>narrateur|Jules choisit bleu. Une feuille tombe. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8136,6 +8180,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8307,6 +8352,7 @@
           <t>narrateur|Jules choisit blanc. On entend des pas. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8474,6 +8520,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8645,6 +8692,7 @@
           <t>narrateur|Jules a choisi le livre. Une feuille tombe. Jules tient le livre contre le manteau de Papa. Il reste près de l'adulte. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8836,6 +8884,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9007,6 +9056,7 @@
           <t>narrateur|Jules choisit jaune. Une feuille tombe. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9174,6 +9224,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9345,6 +9396,7 @@
           <t>narrateur|Jules choisit bleu. On entend des pas. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9512,6 +9564,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9683,6 +9736,7 @@
           <t>narrateur|Jules choisit blanc. Le train souffle loin. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9850,6 +9904,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10021,6 +10076,7 @@
           <t>narrateur|Jules a choisi la dînette. On entend des pas. Jules range la dînette. Il reste près de l'adulte. Main dans la main de Papa. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10212,6 +10268,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10383,6 +10440,7 @@
           <t>narrateur|Jules choisit jaune. On entend des pas. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10550,6 +10608,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10721,6 +10780,7 @@
           <t>narrateur|Jules choisit bleu. Le train souffle loin. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10888,6 +10948,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11059,6 +11120,7 @@
           <t>narrateur|Jules choisit blanc. Un oiseau chante. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11226,6 +11288,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11397,6 +11460,7 @@
           <t>narrateur|Après le train, ils vont près des balançoires. Jules reste près de l'adulte. Main dans la main de Papa, ou sur le manteau. Pieds à côté.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11588,6 +11652,7 @@
           <t>narrateur|On reste où ? Près de l'adulte.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11763,6 +11828,7 @@
           <t>narrateur|Oui. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules retient : près de l'adulte, main ou manteau. La main tient la main de Papa, ou le manteau de Papa. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11954,6 +12020,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12125,6 +12192,7 @@
           <t>narrateur|Jules a choisi les cubes. Le train souffle loin. Jules pose les cubes près de Papa. Il reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12316,6 +12384,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12487,6 +12556,7 @@
           <t>narrateur|Jules choisit jaune. Une feuille tombe. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12654,6 +12724,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12825,6 +12896,7 @@
           <t>narrateur|Jules choisit bleu. On entend des pas. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12992,6 +13064,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13163,6 +13236,7 @@
           <t>narrateur|Jules choisit blanc. Le train souffle loin. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13330,6 +13404,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13501,6 +13576,7 @@
           <t>narrateur|Jules a choisi le livre. Un oiseau chante. Jules tient le livre contre le manteau de Papa. Il reste près de l'adulte. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13692,6 +13768,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13863,6 +13940,7 @@
           <t>narrateur|Jules choisit jaune. On entend des pas. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14030,6 +14108,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14201,6 +14280,7 @@
           <t>narrateur|Jules choisit bleu. Le train souffle loin. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14368,6 +14448,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14539,6 +14620,7 @@
           <t>narrateur|Jules choisit blanc. Un oiseau chante. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14706,6 +14788,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14877,6 +14960,7 @@
           <t>narrateur|Jules a choisi la dînette. Le vent est doux. Jules range la dînette. Il reste près de l'adulte. Main dans la main de Papa. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15068,6 +15152,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15239,6 +15324,7 @@
           <t>narrateur|Jules choisit jaune. Le train souffle loin. Jules choisit le banc jaune. Il reste près de Papa, l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15406,6 +15492,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15577,6 +15664,7 @@
           <t>narrateur|Jules choisit bleu. Un oiseau chante. Jules choisit le banc bleu. Main sur le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15744,6 +15832,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15915,6 +16004,7 @@
           <t>narrateur|Jules choisit blanc. Le vent est doux. Jules choisit le banc blanc. Pieds à côté de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16082,6 +16172,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16100,7 +16191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16124,6 +16215,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16138,7 +16243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16325,6 +16430,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
